--- a/Бухоро_Нафосат опа.xlsx
+++ b/Бухоро_Нафосат опа.xlsx
@@ -5,18 +5,18 @@
   <workbookPr autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shakhrizodaisoeva/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shakhrizodaisoeva/Desktop/Bot data/Prays list/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{24A5D595-D062-714F-B83A-6DA2D3875952}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ED9F188-A691-8946-BAF0-1A91C48D7825}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="21600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="38400" windowHeight="18760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Прайс-лист" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Прайс-лист'!$B$9:$K$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Прайс-лист'!$B$9:$K$13</definedName>
   </definedNames>
   <calcPr calcId="191029" refMode="R1C1"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="27">
   <si>
     <t>МНН</t>
   </si>
@@ -83,19 +83,7 @@
     <t>Реквизиты: OOO «REFLECTIVE MED PHARM» Адрес: 111801, Республика Узбекистан, Ташкентская область, Зангиотинский район, Уртаул коргани, Катта Чинор МФЙ, 1А Р/с20208000905364813002 в «УЗСАНОАТКУРИЛИШБАНКИ» АТБ БОШ ОФИСИ   МФО:00440   ИНН:   308321773.  ОКЭД 46460</t>
   </si>
   <si>
-    <t>Миранол Раствор для внутривенного введения 50мл стеклянные флаконы</t>
-  </si>
-  <si>
-    <t>Эпсол Раствор для инфузий 12 мг/мл 50мл стеклянные флаконы</t>
-  </si>
-  <si>
     <t>Amantadine sulfate</t>
-  </si>
-  <si>
-    <t>Arginine + levocarnitine + citicoline</t>
-  </si>
-  <si>
-    <t>Thioctic acid</t>
   </si>
   <si>
     <t>Pentoxifilinе</t>
@@ -130,9 +118,6 @@
   </si>
   <si>
     <t xml:space="preserve">СП ООО "Reka Med Farm" </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ООО "Temur Med Farm" </t>
   </si>
 </sst>
 </file>
@@ -946,7 +931,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A3:M25"/>
+  <dimension ref="A3:M23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="25"/>
   <cols>
     <col min="1" max="1" width="12" style="1" customWidth="1"/>
@@ -1001,7 +986,7 @@
       <c r="B7" s="19"/>
       <c r="C7" s="19"/>
       <c r="D7" s="32" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E7" s="32"/>
       <c r="F7" s="32"/>
@@ -1029,7 +1014,7 @@
     </row>
     <row r="9" spans="1:13" ht="83.25" customHeight="1">
       <c r="A9" s="20" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B9" s="20" t="s">
         <v>4</v>
@@ -1059,7 +1044,7 @@
         <v>2</v>
       </c>
       <c r="K9" s="22" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="48" customHeight="1">
@@ -1067,13 +1052,13 @@
         <v>1</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D10" s="26">
         <v>500</v>
       </c>
       <c r="E10" s="27" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F10" s="28">
         <v>34982</v>
@@ -1090,10 +1075,10 @@
         <v>46569</v>
       </c>
       <c r="J10" s="26" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="K10" s="29" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:13" s="8" customFormat="1" ht="48" customHeight="1">
@@ -1107,13 +1092,13 @@
         <v>28</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F11" s="28">
         <v>95400</v>
       </c>
       <c r="G11" s="28">
-        <f t="shared" ref="G11:G15" si="1">F11*(1+$G$8%)</f>
+        <f t="shared" ref="G11:G13" si="1">F11*(1+$G$8%)</f>
         <v>109709.99999999999</v>
       </c>
       <c r="H11" s="28">
@@ -1124,10 +1109,10 @@
         <v>46388</v>
       </c>
       <c r="J11" s="26" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="K11" s="29" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="M11" s="15"/>
     </row>
@@ -1142,7 +1127,7 @@
         <v>28</v>
       </c>
       <c r="E12" s="27" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F12" s="28">
         <v>37000</v>
@@ -1152,17 +1137,17 @@
         <v>42550</v>
       </c>
       <c r="H12" s="28">
-        <f t="shared" ref="H12:H15" si="2">+G12*1.12</f>
+        <f t="shared" ref="H12:H13" si="2">+G12*1.12</f>
         <v>47656.000000000007</v>
       </c>
       <c r="I12" s="29">
         <v>46296</v>
       </c>
       <c r="J12" s="26" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="K12" s="29" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="47" customHeight="1">
@@ -1170,173 +1155,105 @@
         <v>4</v>
       </c>
       <c r="C13" s="25" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D13" s="26">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="E13" s="27" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F13" s="28">
-        <v>90000</v>
+        <v>40000</v>
       </c>
       <c r="G13" s="28">
         <f t="shared" si="1"/>
-        <v>103499.99999999999</v>
+        <v>46000</v>
       </c>
       <c r="H13" s="28">
         <f t="shared" si="2"/>
-        <v>115920</v>
+        <v>51520.000000000007</v>
       </c>
       <c r="I13" s="29">
-        <v>46600</v>
+        <v>46661</v>
       </c>
       <c r="J13" s="26" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="K13" s="29" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="47" customHeight="1">
-      <c r="B14" s="24">
-        <v>5</v>
-      </c>
-      <c r="C14" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="D14" s="26">
-        <v>28</v>
-      </c>
-      <c r="E14" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="F14" s="28">
-        <v>40000</v>
-      </c>
-      <c r="G14" s="28">
-        <f t="shared" si="1"/>
-        <v>46000</v>
-      </c>
-      <c r="H14" s="28">
-        <f t="shared" si="2"/>
-        <v>51520.000000000007</v>
-      </c>
-      <c r="I14" s="29">
-        <v>46661</v>
-      </c>
-      <c r="J14" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="K14" s="29" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="40">
-      <c r="B15" s="24">
-        <v>6</v>
-      </c>
-      <c r="C15" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="D15" s="26">
-        <v>50</v>
-      </c>
-      <c r="E15" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="F15" s="28">
-        <v>65000</v>
-      </c>
-      <c r="G15" s="28">
-        <f t="shared" si="1"/>
-        <v>74750</v>
-      </c>
-      <c r="H15" s="28">
-        <f t="shared" si="2"/>
-        <v>83720.000000000015</v>
-      </c>
-      <c r="I15" s="29">
-        <v>46600</v>
-      </c>
-      <c r="J15" s="26" t="s">
-        <v>31</v>
-      </c>
-      <c r="K15" s="29" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13">
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-    </row>
-    <row r="18" spans="2:11" ht="130" customHeight="1">
-      <c r="B18" s="33" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+    </row>
+    <row r="16" spans="1:13" ht="130" customHeight="1">
+      <c r="B16" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="C18" s="33"/>
-      <c r="D18" s="33"/>
-      <c r="E18" s="33"/>
-      <c r="F18" s="33"/>
-      <c r="G18" s="33"/>
-      <c r="H18" s="33"/>
-      <c r="I18" s="33"/>
-      <c r="J18" s="33"/>
-      <c r="K18" s="33"/>
+      <c r="C16" s="33"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="33"/>
+      <c r="H16" s="33"/>
+      <c r="I16" s="33"/>
+      <c r="J16" s="33"/>
+      <c r="K16" s="33"/>
+    </row>
+    <row r="17" spans="2:11">
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
+    </row>
+    <row r="18" spans="2:11">
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1"/>
     </row>
     <row r="19" spans="2:11">
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
+      <c r="K19" s="17"/>
     </row>
     <row r="20" spans="2:11">
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
-      <c r="K20" s="1"/>
+      <c r="K20" s="23"/>
     </row>
     <row r="21" spans="2:11">
-      <c r="K21" s="17"/>
+      <c r="K21" s="23"/>
     </row>
     <row r="22" spans="2:11">
-      <c r="K22" s="23"/>
-    </row>
-    <row r="23" spans="2:11">
-      <c r="K23" s="23"/>
-    </row>
-    <row r="24" spans="2:11">
-      <c r="K24" s="17"/>
-    </row>
-    <row r="25" spans="2:11" ht="25" customHeight="1">
-      <c r="K25" s="1"/>
+      <c r="K22" s="17"/>
+    </row>
+    <row r="23" spans="2:11" ht="25" customHeight="1">
+      <c r="K23" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="B9:K15" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="B9:K13" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="4">
     <mergeCell ref="J8:K8"/>
     <mergeCell ref="D7:H7"/>
-    <mergeCell ref="B18:K18"/>
+    <mergeCell ref="B16:K16"/>
     <mergeCell ref="C6:J6"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
